--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.25655649174408</v>
+        <v>7.354190429908413</v>
       </c>
       <c r="D2" t="n">
-        <v>44.42956947181511</v>
+        <v>7.219805039169956</v>
       </c>
       <c r="E2" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F2" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.59432053921614</v>
+        <v>6.759077087622623</v>
       </c>
       <c r="D3" t="n">
-        <v>42.19199162892171</v>
+        <v>6.856198639699778</v>
       </c>
       <c r="E3" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F3" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.73782666919066</v>
+        <v>8.244896833743482</v>
       </c>
       <c r="D4" t="n">
-        <v>51.57310592592929</v>
+        <v>8.380629712963509</v>
       </c>
       <c r="E4" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F4" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.08152111310073</v>
+        <v>4.888247180878869</v>
       </c>
       <c r="D5" t="n">
-        <v>30.94570641354137</v>
+        <v>5.028677292200474</v>
       </c>
       <c r="E5" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F5" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.0849443571288</v>
+        <v>9.27630345803343</v>
       </c>
       <c r="D6" t="n">
-        <v>34.18762621974739</v>
+        <v>5.55548926070895</v>
       </c>
       <c r="E6" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F6" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.64437271165975</v>
+        <v>9.529710565644709</v>
       </c>
       <c r="D7" t="n">
-        <v>26.37540816263303</v>
+        <v>4.286003826427867</v>
       </c>
       <c r="E7" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F7" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.1208946849028</v>
+        <v>3.594645386296705</v>
       </c>
       <c r="D8" t="n">
-        <v>21.48428941893078</v>
+        <v>3.491197030576251</v>
       </c>
       <c r="E8" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F8" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.02376179487329</v>
+        <v>9.75386129166691</v>
       </c>
       <c r="D9" t="n">
-        <v>18.37924838316584</v>
+        <v>2.98662786226445</v>
       </c>
       <c r="E9" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F9" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.70513720973776</v>
+        <v>7.752084796582387</v>
       </c>
       <c r="D10" t="n">
-        <v>20.34891321037748</v>
+        <v>3.30669839668634</v>
       </c>
       <c r="E10" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F10" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.94683804055307</v>
+        <v>5.353861181589874</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00604004320071</v>
+        <v>5.688481507020116</v>
       </c>
       <c r="E11" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F11" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>59.42971643625741</v>
+        <v>9.657328920891828</v>
       </c>
       <c r="D12" t="n">
-        <v>6.632748474553026</v>
+        <v>1.077821627114867</v>
       </c>
       <c r="E12" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F12" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.96695902482997</v>
+        <v>3.89463084153487</v>
       </c>
       <c r="D13" t="n">
-        <v>27.4055753945635</v>
+        <v>4.453406001616568</v>
       </c>
       <c r="E13" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F13" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.38079483491281</v>
+        <v>2.336879160673333</v>
       </c>
       <c r="D14" t="n">
-        <v>8.894627636844977</v>
+        <v>1.445376990987309</v>
       </c>
       <c r="E14" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F14" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.07987147752283</v>
+        <v>6.51297911509746</v>
       </c>
       <c r="D15" t="n">
-        <v>32.56819266769388</v>
+        <v>5.292331308500255</v>
       </c>
       <c r="E15" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F15" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.30795072751856</v>
+        <v>4.762541993221767</v>
       </c>
       <c r="D16" t="n">
-        <v>34.82954716445229</v>
+        <v>5.659801414223497</v>
       </c>
       <c r="E16" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F16" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.98373500205653</v>
+        <v>7.309856937834187</v>
       </c>
       <c r="D17" t="n">
-        <v>15.02174692233563</v>
+        <v>2.44103387487954</v>
       </c>
       <c r="E17" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F17" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>59.44687049273694</v>
+        <v>9.660116455069753</v>
       </c>
       <c r="D18" t="n">
-        <v>13.87978947080431</v>
+        <v>2.2554657890057</v>
       </c>
       <c r="E18" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F18" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.6328354270732</v>
+        <v>7.902835756899394</v>
       </c>
       <c r="D19" t="n">
-        <v>22.56475291236623</v>
+        <v>3.666772348259512</v>
       </c>
       <c r="E19" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F19" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>58.14989391941243</v>
+        <v>9.449357761904521</v>
       </c>
       <c r="D20" t="n">
-        <v>10.05275875937443</v>
+        <v>1.633573298398345</v>
       </c>
       <c r="E20" t="n">
-        <v>13.965793701384</v>
+        <v>2.269441476474899</v>
       </c>
       <c r="F20" t="n">
-        <v>12.27504341042324</v>
+        <v>1.994694554193776</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
